--- a/etf_holdings/2026-09-14_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-14_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.27%944,000</t>
+          <t>9.21%944,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.21%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.86%427,000</t>
+          <t>5.80%427,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>5.80%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.59%256,000</t>
+          <t>5.61%256,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>5.61%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.97%1,248,000</t>
+          <t>4.96%1,248,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>4.96%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+4.58%6400</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2270</v>
+        <v>6400</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.97%421,644</t>
+          <t>4.07%155,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>421644</v>
+        <v>155000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-1.73%2270</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6400</v>
+        <v>2270</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.86%155,000</t>
+          <t>3.92%421,644</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>155000</v>
+        <v>421644</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.41%613,000</t>
+          <t>3.54%613,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.12%133,000</t>
+          <t>3.17%133,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.00%131,000</t>
+          <t>3.01%131,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.85%325,000</t>
+          <t>2.89%325,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.76%56,000</t>
+          <t>2.75%56,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.73%1,084,000</t>
+          <t>2.72%1,084,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-14 19:17:49</t>
+          <t>2026-09-14 23:58:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.43%368,000</t>
+          <t>2.44%368,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.40%32,900</t>
+          <t>2.43%32,900</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.26%1,019,000</t>
+          <t>2.28%1,019,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.17%80,000</t>
+          <t>1.97%80,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>+4.27%1955</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1235</v>
+        <v>1955</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.90%351,000</t>
+          <t>1.96%245,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>351000</v>
+        <v>245000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>-0.93%2140</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1955</v>
+        <v>2140</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.87%245,000</t>
+          <t>1.81%206,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>245000</v>
+        <v>206000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-7.14%1235</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-7.14%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2140</v>
+        <v>1235</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.81%206,000</t>
+          <t>1.78%351,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>206000</v>
+        <v>351000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.70%386,000</t>
+          <t>1.67%386,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.55%109,000</t>
+          <t>1.51%109,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.49%1,320,000</t>
+          <t>1.50%1,320,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.49%130,000</t>
+          <t>1.46%130,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.48%290,000</t>
+          <t>1.46%290,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-4.06%473</t>
+          <t>-1.11%489.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>473</v>
+        <v>489.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.97%485,000</t>
+          <t>0.96%476,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>485000</v>
+        <v>476000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.11%489.5</t>
+          <t>-4.06%473</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-4.06%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>489.5</v>
+        <v>473</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.96%476,000</t>
+          <t>0.94%485,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>476000</v>
+        <v>485000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.90%246,000</t>
+          <t>0.89%246,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:00</t>
+          <t>2026-09-14 23:58:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+4.43%1415</t>
+          <t>-0.97%1020</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+4.43%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1415</v>
+        <v>1020</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.89%154,000</t>
+          <t>0.88%210,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>154000</v>
+        <v>210000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.68%753</t>
+          <t>+4.43%1415</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.68%</t>
+          <t>+4.43%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>753</v>
+        <v>1415</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.89%277,000</t>
+          <t>0.88%154,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>277000</v>
+        <v>154000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-5.49%2325</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-5.49%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1020</v>
+        <v>2325</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.88%210,000</t>
+          <t>0.86%91,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>210000</v>
+        <v>91000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.49%2325</t>
+          <t>-4.68%753</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-4.68%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2325</v>
+        <v>753</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.86%91,000</t>
+          <t>0.86%277,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>91000</v>
+        <v>277000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.77%344,000</t>
+          <t>0.78%344,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.70%1,535,000</t>
+          <t>0.71%1,535,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.57%54,000</t>
+          <t>0.60%54,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.57%1,000,000</t>
+          <t>0.58%1,000,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.55%195,000</t>
+          <t>0.56%195,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.35%67,000</t>
+          <t>0.33%67,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>2451創見</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.63%1990</t>
+          <t>-0.9%274</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1990</v>
+        <v>274</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.32%39,000</t>
+          <t>0.32%287,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>39000</v>
+        <v>287000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,34 +3127,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2451創見</t>
+          <t>3260威剛</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.9%274</t>
+          <t>-1.11%402.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>274</v>
+        <v>402.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.32%287,000</t>
+          <t>0.31%191,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>287000</v>
+        <v>191000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:12</t>
+          <t>2026-09-14 23:58:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3260威剛</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.11%402.5</t>
+          <t>-3.63%1990</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>402.5</v>
+        <v>1990</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.31%191,000</t>
+          <t>0.31%39,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>191000</v>
+        <v>39000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:23</t>
+          <t>2026-09-14 23:58:17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.22%78,000</t>
+          <t>0.23%78,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:23</t>
+          <t>2026-09-14 23:58:17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.20%94,000</t>
+          <t>0.21%94,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:23</t>
+          <t>2026-09-14 23:58:17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.14%203,000</t>
+          <t>0.13%203,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:23</t>
+          <t>2026-09-14 23:58:17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-14 19:18:23</t>
+          <t>2026-09-14 23:58:17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
